--- a/storage/framework/testing/disks/public/exports/test_export.xlsx
+++ b/storage/framework/testing/disks/public/exports/test_export.xlsx
@@ -7,7 +7,8 @@
     <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Calendar" sheetId="1" r:id="rId4"/>
+    <sheet name="Summary" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
@@ -15,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="50">
   <si>
     <t>Dhaka Bypass Expressway Development Company Ltd. Attendance Record-DBEDC Site Office Employee</t>
   </si>
@@ -120,6 +121,51 @@
   </si>
   <si>
     <t>Remark</t>
+  </si>
+  <si>
+    <t>Dhaka Bypass Expressway Development Company Ltd. — Monthly Attendance Summary</t>
+  </si>
+  <si>
+    <t>Whole-day leave/present model — half-days are not yet split (a half-day may count as a full day).</t>
+  </si>
+  <si>
+    <t>Employee</t>
+  </si>
+  <si>
+    <t>Emp ID</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Present</t>
+  </si>
+  <si>
+    <t>Absent</t>
+  </si>
+  <si>
+    <t>Leave</t>
+  </si>
+  <si>
+    <t>OT Hours</t>
+  </si>
+  <si>
+    <t>Late</t>
+  </si>
+  <si>
+    <t>Holidays Worked</t>
+  </si>
+  <si>
+    <t>Weekly-off Worked</t>
+  </si>
+  <si>
+    <t>Working Days</t>
+  </si>
+  <si>
+    <t>Attendance %</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
   </si>
 </sst>
 </file>
@@ -127,7 +173,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -152,6 +198,15 @@
       <strike val="0"/>
       <u val="none"/>
       <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b val="0"/>
+      <i val="1"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
@@ -197,7 +252,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
@@ -209,6 +264,10 @@
     <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -675,4 +734,116 @@
   </headerFooter>
   <tableParts count="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="10.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="6.998" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="10.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="5.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="9" max="9" width="18.71" bestFit="true" customWidth="true" style="0"/>
+    <col min="10" max="10" width="21.138" bestFit="true" customWidth="true" style="0"/>
+    <col min="11" max="11" width="15.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="12" max="12" width="15.282" bestFit="true" customWidth="true" style="0"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A3:L3"/>
+  </mergeCells>
+  <printOptions gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
+</worksheet>
 </file>